--- a/exclusive_system/templates/analogs_template.xlsx
+++ b/exclusive_system/templates/analogs_template.xlsx
@@ -1010,7 +1010,7 @@
         <v/>
       </c>
       <c r="S21" s="23">
-        <f>IF($O21="","",IFERROR(VLOOKUP($B$10,Параметры!$A$10:$D$12,IF($B$7="Аренда",4,IF($B$14="Премиум",3,2)),FALSE)-VLOOKUP(M21,Параметры!$A$10:$D$12,IF($B$7="Аренда",4,IF($B$14="Премиум",3,2)),FALSE),0))</f>
+        <f>IF($O21="","",IF($B$7="Аренда",0,IFERROR(VLOOKUP($B$10,Параметры!$A$10:$C$11,IF($B$14="Премиум",3,2),FALSE)-VLOOKUP(M21,Параметры!$A$10:$C$11,IF($B$14="Премиум",3,2),FALSE),0)))</f>
         <v/>
       </c>
       <c r="T21" s="24" t="n"/>
@@ -1077,7 +1077,7 @@
         <v/>
       </c>
       <c r="S22" s="23">
-        <f>IF($O22="","",IFERROR(VLOOKUP($B$10,Параметры!$A$10:$D$12,IF($B$7="Аренда",4,IF($B$14="Премиум",3,2)),FALSE)-VLOOKUP(M22,Параметры!$A$10:$D$12,IF($B$7="Аренда",4,IF($B$14="Премиум",3,2)),FALSE),0))</f>
+        <f>IF($O22="","",IF($B$7="Аренда",0,IFERROR(VLOOKUP($B$10,Параметры!$A$10:$C$11,IF($B$14="Премиум",3,2),FALSE)-VLOOKUP(M22,Параметры!$A$10:$C$11,IF($B$14="Премиум",3,2),FALSE),0)))</f>
         <v/>
       </c>
       <c r="T22" s="24" t="n"/>
@@ -1144,7 +1144,7 @@
         <v/>
       </c>
       <c r="S23" s="23">
-        <f>IF($O23="","",IFERROR(VLOOKUP($B$10,Параметры!$A$10:$D$12,IF($B$7="Аренда",4,IF($B$14="Премиум",3,2)),FALSE)-VLOOKUP(M23,Параметры!$A$10:$D$12,IF($B$7="Аренда",4,IF($B$14="Премиум",3,2)),FALSE),0))</f>
+        <f>IF($O23="","",IF($B$7="Аренда",0,IFERROR(VLOOKUP($B$10,Параметры!$A$10:$C$11,IF($B$14="Премиум",3,2),FALSE)-VLOOKUP(M23,Параметры!$A$10:$C$11,IF($B$14="Премиум",3,2),FALSE),0)))</f>
         <v/>
       </c>
       <c r="T23" s="24" t="n"/>
@@ -1211,7 +1211,7 @@
         <v/>
       </c>
       <c r="S24" s="23">
-        <f>IF($O24="","",IFERROR(VLOOKUP($B$10,Параметры!$A$10:$D$12,IF($B$7="Аренда",4,IF($B$14="Премиум",3,2)),FALSE)-VLOOKUP(M24,Параметры!$A$10:$D$12,IF($B$7="Аренда",4,IF($B$14="Премиум",3,2)),FALSE),0))</f>
+        <f>IF($O24="","",IF($B$7="Аренда",0,IFERROR(VLOOKUP($B$10,Параметры!$A$10:$C$11,IF($B$14="Премиум",3,2),FALSE)-VLOOKUP(M24,Параметры!$A$10:$C$11,IF($B$14="Премиум",3,2),FALSE),0)))</f>
         <v/>
       </c>
       <c r="T24" s="24" t="n"/>
@@ -1278,7 +1278,7 @@
         <v/>
       </c>
       <c r="S25" s="23">
-        <f>IF($O25="","",IFERROR(VLOOKUP($B$10,Параметры!$A$10:$D$12,IF($B$7="Аренда",4,IF($B$14="Премиум",3,2)),FALSE)-VLOOKUP(M25,Параметры!$A$10:$D$12,IF($B$7="Аренда",4,IF($B$14="Премиум",3,2)),FALSE),0))</f>
+        <f>IF($O25="","",IF($B$7="Аренда",0,IFERROR(VLOOKUP($B$10,Параметры!$A$10:$C$11,IF($B$14="Премиум",3,2),FALSE)-VLOOKUP(M25,Параметры!$A$10:$C$11,IF($B$14="Премиум",3,2),FALSE),0)))</f>
         <v/>
       </c>
       <c r="T25" s="24" t="n"/>
@@ -1345,7 +1345,7 @@
         <v/>
       </c>
       <c r="S26" s="23">
-        <f>IF($O26="","",IFERROR(VLOOKUP($B$10,Параметры!$A$10:$D$12,IF($B$7="Аренда",4,IF($B$14="Премиум",3,2)),FALSE)-VLOOKUP(M26,Параметры!$A$10:$D$12,IF($B$7="Аренда",4,IF($B$14="Премиум",3,2)),FALSE),0))</f>
+        <f>IF($O26="","",IF($B$7="Аренда",0,IFERROR(VLOOKUP($B$10,Параметры!$A$10:$C$11,IF($B$14="Премиум",3,2),FALSE)-VLOOKUP(M26,Параметры!$A$10:$C$11,IF($B$14="Премиум",3,2),FALSE),0)))</f>
         <v/>
       </c>
       <c r="T26" s="24" t="n"/>
@@ -1412,7 +1412,7 @@
         <v/>
       </c>
       <c r="S27" s="23">
-        <f>IF($O27="","",IFERROR(VLOOKUP($B$10,Параметры!$A$10:$D$12,IF($B$7="Аренда",4,IF($B$14="Премиум",3,2)),FALSE)-VLOOKUP(M27,Параметры!$A$10:$D$12,IF($B$7="Аренда",4,IF($B$14="Премиум",3,2)),FALSE),0))</f>
+        <f>IF($O27="","",IF($B$7="Аренда",0,IFERROR(VLOOKUP($B$10,Параметры!$A$10:$C$11,IF($B$14="Премиум",3,2),FALSE)-VLOOKUP(M27,Параметры!$A$10:$C$11,IF($B$14="Премиум",3,2),FALSE),0)))</f>
         <v/>
       </c>
       <c r="T27" s="24" t="n"/>
@@ -1479,7 +1479,7 @@
         <v/>
       </c>
       <c r="S28" s="23">
-        <f>IF($O28="","",IFERROR(VLOOKUP($B$10,Параметры!$A$10:$D$12,IF($B$7="Аренда",4,IF($B$14="Премиум",3,2)),FALSE)-VLOOKUP(M28,Параметры!$A$10:$D$12,IF($B$7="Аренда",4,IF($B$14="Премиум",3,2)),FALSE),0))</f>
+        <f>IF($O28="","",IF($B$7="Аренда",0,IFERROR(VLOOKUP($B$10,Параметры!$A$10:$C$11,IF($B$14="Премиум",3,2),FALSE)-VLOOKUP(M28,Параметры!$A$10:$C$11,IF($B$14="Премиум",3,2),FALSE),0)))</f>
         <v/>
       </c>
       <c r="T28" s="24" t="n"/>
@@ -1546,7 +1546,7 @@
         <v/>
       </c>
       <c r="S29" s="23">
-        <f>IF($O29="","",IFERROR(VLOOKUP($B$10,Параметры!$A$10:$D$12,IF($B$7="Аренда",4,IF($B$14="Премиум",3,2)),FALSE)-VLOOKUP(M29,Параметры!$A$10:$D$12,IF($B$7="Аренда",4,IF($B$14="Премиум",3,2)),FALSE),0))</f>
+        <f>IF($O29="","",IF($B$7="Аренда",0,IFERROR(VLOOKUP($B$10,Параметры!$A$10:$C$11,IF($B$14="Премиум",3,2),FALSE)-VLOOKUP(M29,Параметры!$A$10:$C$11,IF($B$14="Премиум",3,2),FALSE),0)))</f>
         <v/>
       </c>
       <c r="T29" s="24" t="n"/>
@@ -1613,7 +1613,7 @@
         <v/>
       </c>
       <c r="S30" s="23">
-        <f>IF($O30="","",IFERROR(VLOOKUP($B$10,Параметры!$A$10:$D$12,IF($B$7="Аренда",4,IF($B$14="Премиум",3,2)),FALSE)-VLOOKUP(M30,Параметры!$A$10:$D$12,IF($B$7="Аренда",4,IF($B$14="Премиум",3,2)),FALSE),0))</f>
+        <f>IF($O30="","",IF($B$7="Аренда",0,IFERROR(VLOOKUP($B$10,Параметры!$A$10:$C$11,IF($B$14="Премиум",3,2),FALSE)-VLOOKUP(M30,Параметры!$A$10:$C$11,IF($B$14="Премиум",3,2),FALSE),0)))</f>
         <v/>
       </c>
       <c r="T30" s="24" t="n"/>
@@ -1680,7 +1680,7 @@
         <v/>
       </c>
       <c r="S31" s="23">
-        <f>IF($O31="","",IFERROR(VLOOKUP($B$10,Параметры!$A$10:$D$12,IF($B$7="Аренда",4,IF($B$14="Премиум",3,2)),FALSE)-VLOOKUP(M31,Параметры!$A$10:$D$12,IF($B$7="Аренда",4,IF($B$14="Премиум",3,2)),FALSE),0))</f>
+        <f>IF($O31="","",IF($B$7="Аренда",0,IFERROR(VLOOKUP($B$10,Параметры!$A$10:$C$11,IF($B$14="Премиум",3,2),FALSE)-VLOOKUP(M31,Параметры!$A$10:$C$11,IF($B$14="Премиум",3,2),FALSE),0)))</f>
         <v/>
       </c>
       <c r="T31" s="24" t="n"/>
@@ -1747,7 +1747,7 @@
         <v/>
       </c>
       <c r="S32" s="23">
-        <f>IF($O32="","",IFERROR(VLOOKUP($B$10,Параметры!$A$10:$D$12,IF($B$7="Аренда",4,IF($B$14="Премиум",3,2)),FALSE)-VLOOKUP(M32,Параметры!$A$10:$D$12,IF($B$7="Аренда",4,IF($B$14="Премиум",3,2)),FALSE),0))</f>
+        <f>IF($O32="","",IF($B$7="Аренда",0,IFERROR(VLOOKUP($B$10,Параметры!$A$10:$C$11,IF($B$14="Премиум",3,2),FALSE)-VLOOKUP(M32,Параметры!$A$10:$C$11,IF($B$14="Премиум",3,2),FALSE),0)))</f>
         <v/>
       </c>
       <c r="T32" s="24" t="n"/>
@@ -1814,7 +1814,7 @@
         <v/>
       </c>
       <c r="S33" s="23">
-        <f>IF($O33="","",IFERROR(VLOOKUP($B$10,Параметры!$A$10:$D$12,IF($B$7="Аренда",4,IF($B$14="Премиум",3,2)),FALSE)-VLOOKUP(M33,Параметры!$A$10:$D$12,IF($B$7="Аренда",4,IF($B$14="Премиум",3,2)),FALSE),0))</f>
+        <f>IF($O33="","",IF($B$7="Аренда",0,IFERROR(VLOOKUP($B$10,Параметры!$A$10:$C$11,IF($B$14="Премиум",3,2),FALSE)-VLOOKUP(M33,Параметры!$A$10:$C$11,IF($B$14="Премиум",3,2),FALSE),0)))</f>
         <v/>
       </c>
       <c r="T33" s="24" t="n"/>
@@ -1881,7 +1881,7 @@
         <v/>
       </c>
       <c r="S34" s="23">
-        <f>IF($O34="","",IFERROR(VLOOKUP($B$10,Параметры!$A$10:$D$12,IF($B$7="Аренда",4,IF($B$14="Премиум",3,2)),FALSE)-VLOOKUP(M34,Параметры!$A$10:$D$12,IF($B$7="Аренда",4,IF($B$14="Премиум",3,2)),FALSE),0))</f>
+        <f>IF($O34="","",IF($B$7="Аренда",0,IFERROR(VLOOKUP($B$10,Параметры!$A$10:$C$11,IF($B$14="Премиум",3,2),FALSE)-VLOOKUP(M34,Параметры!$A$10:$C$11,IF($B$14="Премиум",3,2),FALSE),0)))</f>
         <v/>
       </c>
       <c r="T34" s="24" t="n"/>
@@ -1948,7 +1948,7 @@
         <v/>
       </c>
       <c r="S35" s="23">
-        <f>IF($O35="","",IFERROR(VLOOKUP($B$10,Параметры!$A$10:$D$12,IF($B$7="Аренда",4,IF($B$14="Премиум",3,2)),FALSE)-VLOOKUP(M35,Параметры!$A$10:$D$12,IF($B$7="Аренда",4,IF($B$14="Премиум",3,2)),FALSE),0))</f>
+        <f>IF($O35="","",IF($B$7="Аренда",0,IFERROR(VLOOKUP($B$10,Параметры!$A$10:$C$11,IF($B$14="Премиум",3,2),FALSE)-VLOOKUP(M35,Параметры!$A$10:$C$11,IF($B$14="Премиум",3,2),FALSE),0)))</f>
         <v/>
       </c>
       <c r="T35" s="24" t="n"/>
@@ -2015,7 +2015,7 @@
         <v/>
       </c>
       <c r="S36" s="23">
-        <f>IF($O36="","",IFERROR(VLOOKUP($B$10,Параметры!$A$10:$D$12,IF($B$7="Аренда",4,IF($B$14="Премиум",3,2)),FALSE)-VLOOKUP(M36,Параметры!$A$10:$D$12,IF($B$7="Аренда",4,IF($B$14="Премиум",3,2)),FALSE),0))</f>
+        <f>IF($O36="","",IF($B$7="Аренда",0,IFERROR(VLOOKUP($B$10,Параметры!$A$10:$C$11,IF($B$14="Премиум",3,2),FALSE)-VLOOKUP(M36,Параметры!$A$10:$C$11,IF($B$14="Премиум",3,2),FALSE),0)))</f>
         <v/>
       </c>
       <c r="T36" s="24" t="n"/>
@@ -2082,7 +2082,7 @@
         <v/>
       </c>
       <c r="S37" s="23">
-        <f>IF($O37="","",IFERROR(VLOOKUP($B$10,Параметры!$A$10:$D$12,IF($B$7="Аренда",4,IF($B$14="Премиум",3,2)),FALSE)-VLOOKUP(M37,Параметры!$A$10:$D$12,IF($B$7="Аренда",4,IF($B$14="Премиум",3,2)),FALSE),0))</f>
+        <f>IF($O37="","",IF($B$7="Аренда",0,IFERROR(VLOOKUP($B$10,Параметры!$A$10:$C$11,IF($B$14="Премиум",3,2),FALSE)-VLOOKUP(M37,Параметры!$A$10:$C$11,IF($B$14="Премиум",3,2),FALSE),0)))</f>
         <v/>
       </c>
       <c r="T37" s="24" t="n"/>
@@ -2149,7 +2149,7 @@
         <v/>
       </c>
       <c r="S38" s="23">
-        <f>IF($O38="","",IFERROR(VLOOKUP($B$10,Параметры!$A$10:$D$12,IF($B$7="Аренда",4,IF($B$14="Премиум",3,2)),FALSE)-VLOOKUP(M38,Параметры!$A$10:$D$12,IF($B$7="Аренда",4,IF($B$14="Премиум",3,2)),FALSE),0))</f>
+        <f>IF($O38="","",IF($B$7="Аренда",0,IFERROR(VLOOKUP($B$10,Параметры!$A$10:$C$11,IF($B$14="Премиум",3,2),FALSE)-VLOOKUP(M38,Параметры!$A$10:$C$11,IF($B$14="Премиум",3,2),FALSE),0)))</f>
         <v/>
       </c>
       <c r="T38" s="24" t="n"/>
@@ -2216,7 +2216,7 @@
         <v/>
       </c>
       <c r="S39" s="23">
-        <f>IF($O39="","",IFERROR(VLOOKUP($B$10,Параметры!$A$10:$D$12,IF($B$7="Аренда",4,IF($B$14="Премиум",3,2)),FALSE)-VLOOKUP(M39,Параметры!$A$10:$D$12,IF($B$7="Аренда",4,IF($B$14="Премиум",3,2)),FALSE),0))</f>
+        <f>IF($O39="","",IF($B$7="Аренда",0,IFERROR(VLOOKUP($B$10,Параметры!$A$10:$C$11,IF($B$14="Премиум",3,2),FALSE)-VLOOKUP(M39,Параметры!$A$10:$C$11,IF($B$14="Премиум",3,2),FALSE),0)))</f>
         <v/>
       </c>
       <c r="T39" s="24" t="n"/>
@@ -2283,7 +2283,7 @@
         <v/>
       </c>
       <c r="S40" s="23">
-        <f>IF($O40="","",IFERROR(VLOOKUP($B$10,Параметры!$A$10:$D$12,IF($B$7="Аренда",4,IF($B$14="Премиум",3,2)),FALSE)-VLOOKUP(M40,Параметры!$A$10:$D$12,IF($B$7="Аренда",4,IF($B$14="Премиум",3,2)),FALSE),0))</f>
+        <f>IF($O40="","",IF($B$7="Аренда",0,IFERROR(VLOOKUP($B$10,Параметры!$A$10:$C$11,IF($B$14="Премиум",3,2),FALSE)-VLOOKUP(M40,Параметры!$A$10:$C$11,IF($B$14="Премиум",3,2),FALSE),0)))</f>
         <v/>
       </c>
       <c r="T40" s="24" t="n"/>
@@ -2350,7 +2350,7 @@
         <v/>
       </c>
       <c r="S41" s="23">
-        <f>IF($O41="","",IFERROR(VLOOKUP($B$10,Параметры!$A$10:$D$12,IF($B$7="Аренда",4,IF($B$14="Премиум",3,2)),FALSE)-VLOOKUP(M41,Параметры!$A$10:$D$12,IF($B$7="Аренда",4,IF($B$14="Премиум",3,2)),FALSE),0))</f>
+        <f>IF($O41="","",IF($B$7="Аренда",0,IFERROR(VLOOKUP($B$10,Параметры!$A$10:$C$11,IF($B$14="Премиум",3,2),FALSE)-VLOOKUP(M41,Параметры!$A$10:$C$11,IF($B$14="Премиум",3,2),FALSE),0)))</f>
         <v/>
       </c>
       <c r="T41" s="24" t="n"/>
@@ -2417,7 +2417,7 @@
         <v/>
       </c>
       <c r="S42" s="23">
-        <f>IF($O42="","",IFERROR(VLOOKUP($B$10,Параметры!$A$10:$D$12,IF($B$7="Аренда",4,IF($B$14="Премиум",3,2)),FALSE)-VLOOKUP(M42,Параметры!$A$10:$D$12,IF($B$7="Аренда",4,IF($B$14="Премиум",3,2)),FALSE),0))</f>
+        <f>IF($O42="","",IF($B$7="Аренда",0,IFERROR(VLOOKUP($B$10,Параметры!$A$10:$C$11,IF($B$14="Премиум",3,2),FALSE)-VLOOKUP(M42,Параметры!$A$10:$C$11,IF($B$14="Премиум",3,2),FALSE),0)))</f>
         <v/>
       </c>
       <c r="T42" s="24" t="n"/>
@@ -2484,7 +2484,7 @@
         <v/>
       </c>
       <c r="S43" s="23">
-        <f>IF($O43="","",IFERROR(VLOOKUP($B$10,Параметры!$A$10:$D$12,IF($B$7="Аренда",4,IF($B$14="Премиум",3,2)),FALSE)-VLOOKUP(M43,Параметры!$A$10:$D$12,IF($B$7="Аренда",4,IF($B$14="Премиум",3,2)),FALSE),0))</f>
+        <f>IF($O43="","",IF($B$7="Аренда",0,IFERROR(VLOOKUP($B$10,Параметры!$A$10:$C$11,IF($B$14="Премиум",3,2),FALSE)-VLOOKUP(M43,Параметры!$A$10:$C$11,IF($B$14="Премиум",3,2),FALSE),0)))</f>
         <v/>
       </c>
       <c r="T43" s="24" t="n"/>
@@ -2551,7 +2551,7 @@
         <v/>
       </c>
       <c r="S44" s="23">
-        <f>IF($O44="","",IFERROR(VLOOKUP($B$10,Параметры!$A$10:$D$12,IF($B$7="Аренда",4,IF($B$14="Премиум",3,2)),FALSE)-VLOOKUP(M44,Параметры!$A$10:$D$12,IF($B$7="Аренда",4,IF($B$14="Премиум",3,2)),FALSE),0))</f>
+        <f>IF($O44="","",IF($B$7="Аренда",0,IFERROR(VLOOKUP($B$10,Параметры!$A$10:$C$11,IF($B$14="Премиум",3,2),FALSE)-VLOOKUP(M44,Параметры!$A$10:$C$11,IF($B$14="Премиум",3,2),FALSE),0)))</f>
         <v/>
       </c>
       <c r="T44" s="24" t="n"/>
@@ -2618,7 +2618,7 @@
         <v/>
       </c>
       <c r="S45" s="23">
-        <f>IF($O45="","",IFERROR(VLOOKUP($B$10,Параметры!$A$10:$D$12,IF($B$7="Аренда",4,IF($B$14="Премиум",3,2)),FALSE)-VLOOKUP(M45,Параметры!$A$10:$D$12,IF($B$7="Аренда",4,IF($B$14="Премиум",3,2)),FALSE),0))</f>
+        <f>IF($O45="","",IF($B$7="Аренда",0,IFERROR(VLOOKUP($B$10,Параметры!$A$10:$C$11,IF($B$14="Премиум",3,2),FALSE)-VLOOKUP(M45,Параметры!$A$10:$C$11,IF($B$14="Премиум",3,2),FALSE),0)))</f>
         <v/>
       </c>
       <c r="T45" s="24" t="n"/>
@@ -2685,7 +2685,7 @@
         <v/>
       </c>
       <c r="S46" s="23">
-        <f>IF($O46="","",IFERROR(VLOOKUP($B$10,Параметры!$A$10:$D$12,IF($B$7="Аренда",4,IF($B$14="Премиум",3,2)),FALSE)-VLOOKUP(M46,Параметры!$A$10:$D$12,IF($B$7="Аренда",4,IF($B$14="Премиум",3,2)),FALSE),0))</f>
+        <f>IF($O46="","",IF($B$7="Аренда",0,IFERROR(VLOOKUP($B$10,Параметры!$A$10:$C$11,IF($B$14="Премиум",3,2),FALSE)-VLOOKUP(M46,Параметры!$A$10:$C$11,IF($B$14="Премиум",3,2),FALSE),0)))</f>
         <v/>
       </c>
       <c r="T46" s="24" t="n"/>
@@ -2752,7 +2752,7 @@
         <v/>
       </c>
       <c r="S47" s="23">
-        <f>IF($O47="","",IFERROR(VLOOKUP($B$10,Параметры!$A$10:$D$12,IF($B$7="Аренда",4,IF($B$14="Премиум",3,2)),FALSE)-VLOOKUP(M47,Параметры!$A$10:$D$12,IF($B$7="Аренда",4,IF($B$14="Премиум",3,2)),FALSE),0))</f>
+        <f>IF($O47="","",IF($B$7="Аренда",0,IFERROR(VLOOKUP($B$10,Параметры!$A$10:$C$11,IF($B$14="Премиум",3,2),FALSE)-VLOOKUP(M47,Параметры!$A$10:$C$11,IF($B$14="Премиум",3,2),FALSE),0)))</f>
         <v/>
       </c>
       <c r="T47" s="24" t="n"/>
@@ -2819,7 +2819,7 @@
         <v/>
       </c>
       <c r="S48" s="23">
-        <f>IF($O48="","",IFERROR(VLOOKUP($B$10,Параметры!$A$10:$D$12,IF($B$7="Аренда",4,IF($B$14="Премиум",3,2)),FALSE)-VLOOKUP(M48,Параметры!$A$10:$D$12,IF($B$7="Аренда",4,IF($B$14="Премиум",3,2)),FALSE),0))</f>
+        <f>IF($O48="","",IF($B$7="Аренда",0,IFERROR(VLOOKUP($B$10,Параметры!$A$10:$C$11,IF($B$14="Премиум",3,2),FALSE)-VLOOKUP(M48,Параметры!$A$10:$C$11,IF($B$14="Премиум",3,2),FALSE),0)))</f>
         <v/>
       </c>
       <c r="T48" s="24" t="n"/>
@@ -2886,7 +2886,7 @@
         <v/>
       </c>
       <c r="S49" s="23">
-        <f>IF($O49="","",IFERROR(VLOOKUP($B$10,Параметры!$A$10:$D$12,IF($B$7="Аренда",4,IF($B$14="Премиум",3,2)),FALSE)-VLOOKUP(M49,Параметры!$A$10:$D$12,IF($B$7="Аренда",4,IF($B$14="Премиум",3,2)),FALSE),0))</f>
+        <f>IF($O49="","",IF($B$7="Аренда",0,IFERROR(VLOOKUP($B$10,Параметры!$A$10:$C$11,IF($B$14="Премиум",3,2),FALSE)-VLOOKUP(M49,Параметры!$A$10:$C$11,IF($B$14="Премиум",3,2),FALSE),0)))</f>
         <v/>
       </c>
       <c r="T49" s="24" t="n"/>
@@ -2953,7 +2953,7 @@
         <v/>
       </c>
       <c r="S50" s="23">
-        <f>IF($O50="","",IFERROR(VLOOKUP($B$10,Параметры!$A$10:$D$12,IF($B$7="Аренда",4,IF($B$14="Премиум",3,2)),FALSE)-VLOOKUP(M50,Параметры!$A$10:$D$12,IF($B$7="Аренда",4,IF($B$14="Премиум",3,2)),FALSE),0))</f>
+        <f>IF($O50="","",IF($B$7="Аренда",0,IFERROR(VLOOKUP($B$10,Параметры!$A$10:$C$11,IF($B$14="Премиум",3,2),FALSE)-VLOOKUP(M50,Параметры!$A$10:$C$11,IF($B$14="Премиум",3,2),FALSE),0)))</f>
         <v/>
       </c>
       <c r="T50" s="24" t="n"/>
@@ -3020,7 +3020,7 @@
         <v/>
       </c>
       <c r="S51" s="23">
-        <f>IF($O51="","",IFERROR(VLOOKUP($B$10,Параметры!$A$10:$D$12,IF($B$7="Аренда",4,IF($B$14="Премиум",3,2)),FALSE)-VLOOKUP(M51,Параметры!$A$10:$D$12,IF($B$7="Аренда",4,IF($B$14="Премиум",3,2)),FALSE),0))</f>
+        <f>IF($O51="","",IF($B$7="Аренда",0,IFERROR(VLOOKUP($B$10,Параметры!$A$10:$C$11,IF($B$14="Премиум",3,2),FALSE)-VLOOKUP(M51,Параметры!$A$10:$C$11,IF($B$14="Премиум",3,2),FALSE),0)))</f>
         <v/>
       </c>
       <c r="T51" s="24" t="n"/>
@@ -3087,7 +3087,7 @@
         <v/>
       </c>
       <c r="S52" s="23">
-        <f>IF($O52="","",IFERROR(VLOOKUP($B$10,Параметры!$A$10:$D$12,IF($B$7="Аренда",4,IF($B$14="Премиум",3,2)),FALSE)-VLOOKUP(M52,Параметры!$A$10:$D$12,IF($B$7="Аренда",4,IF($B$14="Премиум",3,2)),FALSE),0))</f>
+        <f>IF($O52="","",IF($B$7="Аренда",0,IFERROR(VLOOKUP($B$10,Параметры!$A$10:$C$11,IF($B$14="Премиум",3,2),FALSE)-VLOOKUP(M52,Параметры!$A$10:$C$11,IF($B$14="Премиум",3,2),FALSE),0)))</f>
         <v/>
       </c>
       <c r="T52" s="24" t="n"/>
@@ -3154,7 +3154,7 @@
         <v/>
       </c>
       <c r="S53" s="23">
-        <f>IF($O53="","",IFERROR(VLOOKUP($B$10,Параметры!$A$10:$D$12,IF($B$7="Аренда",4,IF($B$14="Премиум",3,2)),FALSE)-VLOOKUP(M53,Параметры!$A$10:$D$12,IF($B$7="Аренда",4,IF($B$14="Премиум",3,2)),FALSE),0))</f>
+        <f>IF($O53="","",IF($B$7="Аренда",0,IFERROR(VLOOKUP($B$10,Параметры!$A$10:$C$11,IF($B$14="Премиум",3,2),FALSE)-VLOOKUP(M53,Параметры!$A$10:$C$11,IF($B$14="Премиум",3,2),FALSE),0)))</f>
         <v/>
       </c>
       <c r="T53" s="24" t="n"/>
@@ -3221,7 +3221,7 @@
         <v/>
       </c>
       <c r="S54" s="23">
-        <f>IF($O54="","",IFERROR(VLOOKUP($B$10,Параметры!$A$10:$D$12,IF($B$7="Аренда",4,IF($B$14="Премиум",3,2)),FALSE)-VLOOKUP(M54,Параметры!$A$10:$D$12,IF($B$7="Аренда",4,IF($B$14="Премиум",3,2)),FALSE),0))</f>
+        <f>IF($O54="","",IF($B$7="Аренда",0,IFERROR(VLOOKUP($B$10,Параметры!$A$10:$C$11,IF($B$14="Премиум",3,2),FALSE)-VLOOKUP(M54,Параметры!$A$10:$C$11,IF($B$14="Премиум",3,2),FALSE),0)))</f>
         <v/>
       </c>
       <c r="T54" s="24" t="n"/>
@@ -3288,7 +3288,7 @@
         <v/>
       </c>
       <c r="S55" s="23">
-        <f>IF($O55="","",IFERROR(VLOOKUP($B$10,Параметры!$A$10:$D$12,IF($B$7="Аренда",4,IF($B$14="Премиум",3,2)),FALSE)-VLOOKUP(M55,Параметры!$A$10:$D$12,IF($B$7="Аренда",4,IF($B$14="Премиум",3,2)),FALSE),0))</f>
+        <f>IF($O55="","",IF($B$7="Аренда",0,IFERROR(VLOOKUP($B$10,Параметры!$A$10:$C$11,IF($B$14="Премиум",3,2),FALSE)-VLOOKUP(M55,Параметры!$A$10:$C$11,IF($B$14="Премиум",3,2),FALSE),0)))</f>
         <v/>
       </c>
       <c r="T55" s="24" t="n"/>
@@ -3355,7 +3355,7 @@
         <v/>
       </c>
       <c r="S56" s="23">
-        <f>IF($O56="","",IFERROR(VLOOKUP($B$10,Параметры!$A$10:$D$12,IF($B$7="Аренда",4,IF($B$14="Премиум",3,2)),FALSE)-VLOOKUP(M56,Параметры!$A$10:$D$12,IF($B$7="Аренда",4,IF($B$14="Премиум",3,2)),FALSE),0))</f>
+        <f>IF($O56="","",IF($B$7="Аренда",0,IFERROR(VLOOKUP($B$10,Параметры!$A$10:$C$11,IF($B$14="Премиум",3,2),FALSE)-VLOOKUP(M56,Параметры!$A$10:$C$11,IF($B$14="Премиум",3,2),FALSE),0)))</f>
         <v/>
       </c>
       <c r="T56" s="24" t="n"/>
@@ -3422,7 +3422,7 @@
         <v/>
       </c>
       <c r="S57" s="23">
-        <f>IF($O57="","",IFERROR(VLOOKUP($B$10,Параметры!$A$10:$D$12,IF($B$7="Аренда",4,IF($B$14="Премиум",3,2)),FALSE)-VLOOKUP(M57,Параметры!$A$10:$D$12,IF($B$7="Аренда",4,IF($B$14="Премиум",3,2)),FALSE),0))</f>
+        <f>IF($O57="","",IF($B$7="Аренда",0,IFERROR(VLOOKUP($B$10,Параметры!$A$10:$C$11,IF($B$14="Премиум",3,2),FALSE)-VLOOKUP(M57,Параметры!$A$10:$C$11,IF($B$14="Премиум",3,2),FALSE),0)))</f>
         <v/>
       </c>
       <c r="T57" s="24" t="n"/>
@@ -3489,7 +3489,7 @@
         <v/>
       </c>
       <c r="S58" s="23">
-        <f>IF($O58="","",IFERROR(VLOOKUP($B$10,Параметры!$A$10:$D$12,IF($B$7="Аренда",4,IF($B$14="Премиум",3,2)),FALSE)-VLOOKUP(M58,Параметры!$A$10:$D$12,IF($B$7="Аренда",4,IF($B$14="Премиум",3,2)),FALSE),0))</f>
+        <f>IF($O58="","",IF($B$7="Аренда",0,IFERROR(VLOOKUP($B$10,Параметры!$A$10:$C$11,IF($B$14="Премиум",3,2),FALSE)-VLOOKUP(M58,Параметры!$A$10:$C$11,IF($B$14="Премиум",3,2),FALSE),0)))</f>
         <v/>
       </c>
       <c r="T58" s="24" t="n"/>
@@ -3556,7 +3556,7 @@
         <v/>
       </c>
       <c r="S59" s="23">
-        <f>IF($O59="","",IFERROR(VLOOKUP($B$10,Параметры!$A$10:$D$12,IF($B$7="Аренда",4,IF($B$14="Премиум",3,2)),FALSE)-VLOOKUP(M59,Параметры!$A$10:$D$12,IF($B$7="Аренда",4,IF($B$14="Премиум",3,2)),FALSE),0))</f>
+        <f>IF($O59="","",IF($B$7="Аренда",0,IFERROR(VLOOKUP($B$10,Параметры!$A$10:$C$11,IF($B$14="Премиум",3,2),FALSE)-VLOOKUP(M59,Параметры!$A$10:$C$11,IF($B$14="Премиум",3,2),FALSE),0)))</f>
         <v/>
       </c>
       <c r="T59" s="24" t="n"/>
@@ -3623,7 +3623,7 @@
         <v/>
       </c>
       <c r="S60" s="23">
-        <f>IF($O60="","",IFERROR(VLOOKUP($B$10,Параметры!$A$10:$D$12,IF($B$7="Аренда",4,IF($B$14="Премиум",3,2)),FALSE)-VLOOKUP(M60,Параметры!$A$10:$D$12,IF($B$7="Аренда",4,IF($B$14="Премиум",3,2)),FALSE),0))</f>
+        <f>IF($O60="","",IF($B$7="Аренда",0,IFERROR(VLOOKUP($B$10,Параметры!$A$10:$C$11,IF($B$14="Премиум",3,2),FALSE)-VLOOKUP(M60,Параметры!$A$10:$C$11,IF($B$14="Премиум",3,2),FALSE),0)))</f>
         <v/>
       </c>
       <c r="T60" s="24" t="n"/>
@@ -3674,10 +3674,10 @@
       <formula1>"Активно,Снято,Сделка"</formula1>
     </dataValidation>
     <dataValidation sqref="M21:M60" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
-      <formula1>Параметры!$A$10:$A$12</formula1>
+      <formula1>Параметры!$A$10:$A$11</formula1>
     </dataValidation>
     <dataValidation sqref="B10" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
-      <formula1>Параметры!$A$10:$A$12</formula1>
+      <formula1>Параметры!$A$10:$A$11</formula1>
     </dataValidation>
     <dataValidation sqref="B14" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>"Комфорт,Премиум"</formula1>
@@ -3696,7 +3696,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D19"/>
+  <dimension ref="A1:C19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="70" customWidth="1" min="1" max="1"/>
@@ -3755,7 +3755,7 @@
     <row r="8">
       <c r="A8" s="4" t="inlineStr">
         <is>
-          <t>РЕМОНТ — стоимость отделки от нуля, БЕЗ мебели (класс объекта — в блоке «Наш объект»)</t>
+          <t>РЕМОНТ (ПРОДАЖА) — стоимость ремонта от нуля, БЕЗ мебели (класс объекта — в блоке «Наш объект»)</t>
         </is>
       </c>
     </row>
@@ -3775,11 +3775,6 @@
           <t>Премиум, ₽ за м²</t>
         </is>
       </c>
-      <c r="D9" s="28" t="inlineStr">
-        <is>
-          <t>Аренда, ₽ за м² в месяц</t>
-        </is>
-      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -3793,46 +3788,31 @@
       <c r="C10" s="12" t="n">
         <v>0</v>
       </c>
-      <c r="D10" s="12" t="n">
-        <v>0</v>
-      </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Предчистовая (white box)</t>
+          <t>С ремонтом (без мебели)</t>
         </is>
       </c>
       <c r="B11" s="12" t="n">
-        <v>12000</v>
+        <v>100000</v>
       </c>
       <c r="C11" s="12" t="n">
-        <v>12000</v>
-      </c>
-      <c r="D11" s="12" t="n">
-        <v>50</v>
+        <v>250000</v>
       </c>
     </row>
     <row r="12">
-      <c r="A12" t="inlineStr">
-        <is>
-          <t>С ремонтом (без мебели)</t>
-        </is>
-      </c>
-      <c r="B12" s="12" t="n">
-        <v>100000</v>
-      </c>
-      <c r="C12" s="12" t="n">
-        <v>250000</v>
-      </c>
-      <c r="D12" s="12" t="n">
-        <v>150</v>
+      <c r="A12" s="2" t="inlineStr">
+        <is>
+          <t>Мебель и техника в корректировку ремонта не входят — если у аналога есть мебель, это ручная корректировка «Прочее».</t>
+        </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="2" t="inlineStr">
         <is>
-          <t>Мебель и техника в корректировку ремонта не входят — если у аналога есть мебель, это ручная корректировка «Прочее».</t>
+          <t>Аренда: автоматической поправки на ремонт нет — ставку в месяц берём из объявлений ЦИАН, разницу в ремонте брокер ставит вручную («Прочее», %).</t>
         </is>
       </c>
     </row>
@@ -3916,7 +3896,7 @@
     <row r="3">
       <c r="A3" s="6" t="inlineStr">
         <is>
-          <t>2. Заполните блок «Наш объект» (сделка, площадь, ремонт, класс — обязательно). Ремонт: комфорт — 100 000 ₽/м², премиум — 250 000 ₽/м², без мебели.</t>
+          <t>2. Заполните блок «Наш объект» (сделка, площадь, ремонт, класс — обязательно). Ремонт (продажа): комфорт — 100 000 ₽/м², премиум — 250 000 ₽/м², без мебели. Аренда — ставка в месяц из ЦИАН, ремонт вручную.</t>
         </is>
       </c>
     </row>
